--- a/Excel/Cell_reference.xlsx
+++ b/Excel/Cell_reference.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{B047973B-8C25-4885-AAB6-F48C5AFA3B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="3" xr2:uid="{DF1973C5-90C4-430C-B5F3-1FE07900EC20}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{DF1973C5-90C4-430C-B5F3-1FE07900EC20}"/>
   </bookViews>
   <sheets>
     <sheet name="Relative cell Reference" sheetId="1" r:id="rId1"/>
